--- a/public/data/ASAMBLEA_DELEGADOS_PROSALUD.xlsx
+++ b/public/data/ASAMBLEA_DELEGADOS_PROSALUD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACaro\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanpabon/Desktop/U/Personal/prosalud/public/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDEEAE3A-9E68-4B0A-9FDA-A5FB9AE68507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36558ED6-63A8-DC43-AC9A-3FF057885F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{76A3B645-9D22-42AF-92C7-FA4091A58662}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15840" xr2:uid="{76A3B645-9D22-42AF-92C7-FA4091A58662}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="86">
   <si>
     <t>CEDULA</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>ZULUAGA DUQUE MARY LUZ</t>
+  </si>
+  <si>
+    <t>GUSTAVO BOTERO ARISTIZABAL</t>
   </si>
 </sst>
 </file>
@@ -384,33 +387,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -450,9 +451,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -490,7 +491,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -596,7 +597,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -738,7 +739,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -746,17 +747,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7674C110-2F0A-4764-B258-891063F572BF}">
-  <dimension ref="A1:D81"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D82"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="47.5703125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="11.42578125" style="3"/>
+    <col min="2" max="2" width="47.5" style="3" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="11.5" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -770,7 +771,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>98641292</v>
       </c>
@@ -784,7 +785,7 @@
         <v>34150</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>1020490811</v>
       </c>
@@ -798,7 +799,7 @@
         <v>42802</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>1045019181</v>
       </c>
@@ -812,7 +813,7 @@
         <v>39322</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>31583955</v>
       </c>
@@ -826,7 +827,7 @@
         <v>36348</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>1152701406</v>
       </c>
@@ -840,7 +841,7 @@
         <v>41591</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>1128480393</v>
       </c>
@@ -854,7 +855,7 @@
         <v>40310</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>71396099</v>
       </c>
@@ -868,7 +869,7 @@
         <v>34505</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>70327253</v>
       </c>
@@ -878,11 +879,11 @@
       <c r="C9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="7">
         <v>35054</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>43713424</v>
       </c>
@@ -896,7 +897,7 @@
         <v>34638</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>1036956665</v>
       </c>
@@ -910,7 +911,7 @@
         <v>41793</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>1214725061</v>
       </c>
@@ -924,7 +925,7 @@
         <v>41120</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>1017137676</v>
       </c>
@@ -938,7 +939,7 @@
         <v>38260</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>45538784</v>
       </c>
@@ -952,7 +953,7 @@
         <v>36713</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>1024475280</v>
       </c>
@@ -966,7 +967,7 @@
         <v>38586</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>1017229234</v>
       </c>
@@ -980,7 +981,7 @@
         <v>41369</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>15259573</v>
       </c>
@@ -994,7 +995,7 @@
         <v>30932</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>1020472681</v>
       </c>
@@ -1008,7 +1009,7 @@
         <v>41585</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>1000918728</v>
       </c>
@@ -1022,7 +1023,7 @@
         <v>43201</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>1036944216</v>
       </c>
@@ -1036,7 +1037,7 @@
         <v>40410</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>1037615030</v>
       </c>
@@ -1050,7 +1051,7 @@
         <v>40036</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>1076383524</v>
       </c>
@@ -1064,7 +1065,7 @@
         <v>40092</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>98489067</v>
       </c>
@@ -1078,7 +1079,7 @@
         <v>30403</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>1036967477</v>
       </c>
@@ -1092,7 +1093,7 @@
         <v>43115</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>70698615</v>
       </c>
@@ -1106,7 +1107,7 @@
         <v>37690</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>1143376178</v>
       </c>
@@ -1120,7 +1121,7 @@
         <v>41151</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>30239874</v>
       </c>
@@ -1134,7 +1135,7 @@
         <v>37467</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>43858854</v>
       </c>
@@ -1148,7 +1149,7 @@
         <v>36047</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>1193034274</v>
       </c>
@@ -1162,7 +1163,7 @@
         <v>42759</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="11">
         <v>1036943214</v>
       </c>
@@ -1176,7 +1177,7 @@
         <v>40283</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>1035428555</v>
       </c>
@@ -1190,7 +1191,7 @@
         <v>40480</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>1037236437</v>
       </c>
@@ -1204,7 +1205,7 @@
         <v>38889</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>1128280862</v>
       </c>
@@ -1218,7 +1219,7 @@
         <v>39412</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>1036397271</v>
       </c>
@@ -1232,7 +1233,7 @@
         <v>40317</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>43048052</v>
       </c>
@@ -1246,7 +1247,7 @@
         <v>29684</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>43640877</v>
       </c>
@@ -1260,7 +1261,7 @@
         <v>35310</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>43688582</v>
       </c>
@@ -1274,7 +1275,7 @@
         <v>35408</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>1088264331</v>
       </c>
@@ -1288,7 +1289,7 @@
         <v>39104</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>1143158713</v>
       </c>
@@ -1302,7 +1303,7 @@
         <v>41968</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>1035430385</v>
       </c>
@@ -1316,7 +1317,7 @@
         <v>40779</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>1128461596</v>
       </c>
@@ -1330,7 +1331,7 @@
         <v>41656</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>1146440977</v>
       </c>
@@ -1344,7 +1345,7 @@
         <v>42059</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>1052410279</v>
       </c>
@@ -1358,7 +1359,7 @@
         <v>42174</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>1039460962</v>
       </c>
@@ -1372,7 +1373,7 @@
         <v>40889</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>1040322531</v>
       </c>
@@ -1386,7 +1387,7 @@
         <v>39652</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>1007942369</v>
       </c>
@@ -1400,7 +1401,7 @@
         <v>44568</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>1036929650</v>
       </c>
@@ -1414,7 +1415,7 @@
         <v>38705</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>71314181</v>
       </c>
@@ -1428,7 +1429,7 @@
         <v>36025</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>35546990</v>
       </c>
@@ -1442,7 +1443,7 @@
         <v>37843</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>1001745429</v>
       </c>
@@ -1456,7 +1457,7 @@
         <v>42548</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>43184024</v>
       </c>
@@ -1470,7 +1471,7 @@
         <v>37134</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>1075244873</v>
       </c>
@@ -1484,7 +1485,7 @@
         <v>39618</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>43498067</v>
       </c>
@@ -1498,7 +1499,7 @@
         <v>30951</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>1128436059</v>
       </c>
@@ -1512,7 +1513,7 @@
         <v>39832</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>1037524346</v>
       </c>
@@ -1526,7 +1527,7 @@
         <v>39224</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>1083570756</v>
       </c>
@@ -1540,7 +1541,7 @@
         <v>40998</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>1028035623</v>
       </c>
@@ -1554,7 +1555,7 @@
         <v>42548</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>71741338</v>
       </c>
@@ -1568,7 +1569,7 @@
         <v>33672</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>1152219272</v>
       </c>
@@ -1582,7 +1583,7 @@
         <v>42335</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>1035865928</v>
       </c>
@@ -1596,7 +1597,7 @@
         <v>40837</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>21533966</v>
       </c>
@@ -1610,7 +1611,7 @@
         <v>37270</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>1036619068</v>
       </c>
@@ -1624,7 +1625,7 @@
         <v>39038</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>1002061230</v>
       </c>
@@ -1638,7 +1639,7 @@
         <v>43685</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>1041531237</v>
       </c>
@@ -1652,7 +1653,7 @@
         <v>44895</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>73190564</v>
       </c>
@@ -1666,7 +1667,7 @@
         <v>36714</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>1045050134</v>
       </c>
@@ -1680,7 +1681,7 @@
         <v>41809</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>32221039</v>
       </c>
@@ -1694,7 +1695,7 @@
         <v>37903</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>1035229453</v>
       </c>
@@ -1708,7 +1709,7 @@
         <v>40884</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <v>1062396550</v>
       </c>
@@ -1722,7 +1723,7 @@
         <v>38929</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>1093212304</v>
       </c>
@@ -1736,7 +1737,7 @@
         <v>38091</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>1036954374</v>
       </c>
@@ -1750,7 +1751,7 @@
         <v>41548</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>1036935300</v>
       </c>
@@ -1764,7 +1765,7 @@
         <v>39346</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>39433850</v>
       </c>
@@ -1778,7 +1779,7 @@
         <v>29096</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>1037630247</v>
       </c>
@@ -1792,7 +1793,7 @@
         <v>40876</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
         <v>1214723971</v>
       </c>
@@ -1806,7 +1807,7 @@
         <v>41043</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>1039467286</v>
       </c>
@@ -1820,7 +1821,7 @@
         <v>41822</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>1062400695</v>
       </c>
@@ -1834,7 +1835,7 @@
         <v>40707</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="6">
         <v>1035414901</v>
       </c>
@@ -1848,7 +1849,7 @@
         <v>38187</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <v>1100689245</v>
       </c>
@@ -1862,7 +1863,7 @@
         <v>40555</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
         <v>71727074</v>
       </c>
@@ -1876,7 +1877,7 @@
         <v>33057</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>1045017059</v>
       </c>
@@ -1888,6 +1889,20 @@
       </c>
       <c r="D81" s="7">
         <v>38412</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>71583039</v>
+      </c>
+      <c r="B82" t="s">
+        <v>85</v>
+      </c>
+      <c r="C82" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82" s="12">
+        <v>28740</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/ASAMBLEA_DELEGADOS_PROSALUD.xlsx
+++ b/public/data/ASAMBLEA_DELEGADOS_PROSALUD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanpabon/Desktop/U/Personal/prosalud/public/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36558ED6-63A8-DC43-AC9A-3FF057885F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087C97E3-5E82-7C40-9F7B-7574B9850493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15840" xr2:uid="{76A3B645-9D22-42AF-92C7-FA4091A58662}"/>
   </bookViews>
@@ -376,7 +376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -411,12 +411,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1891,26 +1900,26 @@
         <v>38412</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82">
+    <row r="82" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A82" s="4">
         <v>71583039</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C82" t="s">
-        <v>4</v>
-      </c>
-      <c r="D82" s="12">
+      <c r="C82" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82" s="7">
         <v>28740</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A80">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A81">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="A81:A82">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/ASAMBLEA_DELEGADOS_PROSALUD.xlsx
+++ b/public/data/ASAMBLEA_DELEGADOS_PROSALUD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanpabon/Desktop/U/Personal/prosalud/public/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087C97E3-5E82-7C40-9F7B-7574B9850493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811998CF-9897-E440-A67E-16DC02303037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="15840" xr2:uid="{76A3B645-9D22-42AF-92C7-FA4091A58662}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="90">
   <si>
     <t>CEDULA</t>
   </si>
@@ -283,6 +283,18 @@
   </si>
   <si>
     <t>GUSTAVO BOTERO ARISTIZABAL</t>
+  </si>
+  <si>
+    <t>MARIA CAMILA MARTINEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalina María Murcia </t>
+  </si>
+  <si>
+    <t>Diana María Argumedo Esquivel</t>
+  </si>
+  <si>
+    <t>Leidy mesa hincapié</t>
   </si>
 </sst>
 </file>
@@ -415,7 +427,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -756,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7674C110-2F0A-4764-B258-891063F572BF}">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" style="3" bestFit="1" customWidth="1"/>
@@ -1914,12 +1936,71 @@
         <v>28740</v>
       </c>
     </row>
+    <row r="83" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A83" s="4">
+        <v>1037637317</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D83" s="7">
+        <v>41224</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A84" s="4">
+        <v>43400882</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D84" s="7">
+        <v>36242</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A85" s="4">
+        <v>1067854298</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D85" s="7">
+        <v>38610</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A86" s="4">
+        <v>1017217553</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D86" s="7">
+        <v>40994</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A80">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A81:A83">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A81:A82">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  <conditionalFormatting sqref="A84:A86">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
